--- a/filtered_scenarios.xlsx
+++ b/filtered_scenarios.xlsx
@@ -10,8 +10,14 @@
     <sheet name="color codes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="all_scenarios" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="green-green" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="yellow-green" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="red-green" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="green-yellow" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="green-red" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="yellow-green" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="yellow-yellow" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="yellow-red" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="red-green" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="red-yellow" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="red-red" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,6 +461,574 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>scenario-id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>scenario-text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>scenario-url</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>body-area</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>priority-clinical-areas</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ct_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ct_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ct_not_appropriate</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>other_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>other_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>other_not_appropriate</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>mr_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>mr_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mr_not_appropriate</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>us_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>us_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>us_not_appropriate</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>other_modality_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>other_modality_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>other_modality_not_appropriate</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>green-green</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>green-yellow</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>green-red</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>yellow-green</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>yellow-yellow</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>yellow-red</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>red-green</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>red-yellow</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>red-red</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>scenario-id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>scenario-text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>scenario-url</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>body-area</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>priority-clinical-areas</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ct_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ct_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ct_not_appropriate</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>other_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>other_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>other_not_appropriate</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>mr_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>mr_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mr_not_appropriate</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>us_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>us_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>us_not_appropriate</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>other_modality_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>other_modality_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>other_modality_not_appropriate</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>green-green</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>green-yellow</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>green-red</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>yellow-green</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>yellow-yellow</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>yellow-red</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>red-green</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>red-yellow</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>red-red</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Urologic</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3195297</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pyelonephritis suspected, acute, uncomplicated, first time presentation, initial imaging</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6245</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Abdomen-pelvis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Urologic</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3074311</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>UTI, lower urinary tract, recurrent, uncomplicated, no risk factors</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=1004</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Female Only</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Abdomen-pelvis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -37305,7 +37879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF33"/>
+  <dimension ref="A1:AF47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37477,16 +38051,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3196526</v>
+        <v>3081311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Abnormal liver function tests, hepatocellular predominance, mild aminotransferase increase , initial imaging</t>
+          <t>Abd pain, acute, nonlocalized, fever, initial exam</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7151</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=1133</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -37501,21 +38075,21 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -37533,34 +38107,34 @@
         <v>0</v>
       </c>
       <c r="R2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="b">
         <v>1</v>
       </c>
       <c r="T2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="b">
         <v>0</v>
       </c>
       <c r="Y2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
       </c>
       <c r="AA2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="b">
         <v>0</v>
@@ -37585,16 +38159,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3194197</v>
+        <v>3074175</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Epigastric pain, acid reflux suspected, initial imaging</t>
+          <t>Abd pain, acute, nonlocalized, fever, post op, initial exam</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5564</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=883</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -37609,21 +38183,21 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
@@ -37635,22 +38209,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
@@ -37662,13 +38236,13 @@
         <v>0</v>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
       </c>
       <c r="AA3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="b">
         <v>0</v>
@@ -37693,16 +38267,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3194201</v>
+        <v>3141528</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Epigastric pain, duodenal ulcer suspected, initial imaging</t>
+          <t>Abd pain, acute, nonlocalized, neutropenic, initial exam</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5568</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=3566</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -37717,21 +38291,21 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
@@ -37743,25 +38317,25 @@
         <v>0</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="b">
         <v>1</v>
@@ -37770,13 +38344,13 @@
         <v>0</v>
       </c>
       <c r="Y4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
       </c>
       <c r="AA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="b">
         <v>0</v>
@@ -37801,16 +38375,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3194198</v>
+        <v>3411</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Epigastric pain, esophagitis suspected, initial imaging</t>
+          <t>Abscess, liver</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5565</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=495</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -37830,7 +38404,7 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -37839,7 +38413,7 @@
         <v>1</v>
       </c>
       <c r="L5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -37851,25 +38425,25 @@
         <v>0</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="b">
         <v>1</v>
@@ -37878,13 +38452,13 @@
         <v>0</v>
       </c>
       <c r="Y5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
       </c>
       <c r="AA5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="b">
         <v>0</v>
@@ -37909,16 +38483,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3194199</v>
+        <v>3195290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Epigastric pain, gastritis suspected, initial imaging</t>
+          <t>Diaphragmatic hernia suspected, Bochdalek, initial imaging</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5566</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6241</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -37933,21 +38507,21 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Chest-abdomen</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -37959,10 +38533,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -37971,10 +38545,10 @@
         <v>0</v>
       </c>
       <c r="T6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
@@ -37986,13 +38560,13 @@
         <v>0</v>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AA6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="b">
         <v>0</v>
@@ -38017,16 +38591,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3194200</v>
+        <v>3195291</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Epigastric pain, peptic ulcer suspected, initial imaging</t>
+          <t>Diaphragmatic hernia suspected, Morgagni, initial imaging</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5567</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6242</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -38041,21 +38615,21 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Chest-abdomen</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
@@ -38067,10 +38641,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -38079,10 +38653,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
@@ -38094,13 +38668,13 @@
         <v>0</v>
       </c>
       <c r="Y7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
       </c>
       <c r="AA7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="b">
         <v>0</v>
@@ -38125,16 +38699,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3100710</v>
+        <v>3195289</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Liver lesion, &lt;1cm, indeterminate on US, hx of extrahepatic malignancy</t>
+          <t>Diaphragmatic hernia suspected, traumatic, initial imaging</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2164</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6240</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -38149,21 +38723,21 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Chest-abdomen</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -38172,7 +38746,7 @@
         <v>1</v>
       </c>
       <c r="O8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
@@ -38184,16 +38758,16 @@
         <v>0</v>
       </c>
       <c r="S8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="b">
         <v>1</v>
@@ -38202,13 +38776,13 @@
         <v>0</v>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="b">
         <v>0</v>
@@ -38233,16 +38807,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3084079</v>
+        <v>3196472</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pancreatitis suspected, typical presentation</t>
+          <t>LLQ pain, diverticulitis complications suspected, initial imaging</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2103</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7112</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -38262,7 +38836,7 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -38271,7 +38845,7 @@
         <v>1</v>
       </c>
       <c r="L9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -38289,10 +38863,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="b">
         <v>1</v>
@@ -38301,22 +38875,22 @@
         <v>0</v>
       </c>
       <c r="V9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="b">
         <v>0</v>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
       </c>
       <c r="AA9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="b">
         <v>0</v>
@@ -38341,16 +38915,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3195883</v>
+        <v>3196471</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RUQ pain, acalculous cholecystitis suspected, US equivocal, next imaging study</t>
+          <t>LLQ pain, diverticulitis suspected, initial imaging</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6707</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7111</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -38370,7 +38944,7 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -38379,13 +38953,13 @@
         <v>1</v>
       </c>
       <c r="L10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="b">
         <v>1</v>
       </c>
       <c r="N10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
@@ -38403,28 +38977,28 @@
         <v>0</v>
       </c>
       <c r="T10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="b">
         <v>0</v>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
       </c>
       <c r="AA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="b">
         <v>0</v>
@@ -38449,16 +39023,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3195882</v>
+        <v>3196470</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RUQ pain, acalculous cholecystitis suspected, US negative, next imaging study</t>
+          <t>LLQ pain, initial imaging</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6706</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7110</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -38478,7 +39052,7 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -38487,13 +39061,13 @@
         <v>1</v>
       </c>
       <c r="L11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="b">
         <v>1</v>
       </c>
       <c r="N11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
@@ -38508,31 +39082,31 @@
         <v>0</v>
       </c>
       <c r="S11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
       </c>
       <c r="U11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
       </c>
       <c r="W11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="b">
         <v>0</v>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
       </c>
       <c r="AA11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="b">
         <v>0</v>
@@ -38557,16 +39131,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3195877</v>
+        <v>3141499</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RUQ pain, biliary disease suspected, initial imaging</t>
+          <t>Mesenteric ischemia, acute, suspected, initial exam</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6701</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=3537</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -38581,12 +39155,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -38595,13 +39169,13 @@
         <v>1</v>
       </c>
       <c r="L12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="b">
         <v>1</v>
       </c>
       <c r="N12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -38610,13 +39184,13 @@
         <v>1</v>
       </c>
       <c r="Q12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
@@ -38634,13 +39208,13 @@
         <v>0</v>
       </c>
       <c r="Y12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
       </c>
       <c r="AA12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="b">
         <v>0</v>
@@ -38661,49 +39235,49 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gyn and OB</t>
+          <t>Gastrointestinal</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3074377</v>
+        <v>3084081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pelvic pain, acute, negative beta-hCG, gynecological etiology suspected, initial imaging</t>
+          <t>Pancreatitis necrotizing, significant clinical deterioration</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=1042</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2105</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Female Only</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10 - 60</t>
+          <t>18 - 150</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelvis</t>
+          <t>Abdomen</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="b">
         <v>1</v>
@@ -38718,16 +39292,16 @@
         <v>1</v>
       </c>
       <c r="Q13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
@@ -38742,13 +39316,13 @@
         <v>0</v>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
       </c>
       <c r="AA13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="b">
         <v>0</v>
@@ -38769,25 +39343,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gyn and OB</t>
+          <t>Gastrointestinal</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3148178</v>
+        <v>3195406</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pelvic pain, chronic, post-menopausal</t>
+          <t>RLQ pain, fever, leukocytosis, appendicitis suspected, initial imaging</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=4553</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6315</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Female Only</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -38797,12 +39371,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelvis</t>
+          <t>Abdomen</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -38811,7 +39385,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="b">
         <v>1</v>
@@ -38829,10 +39403,10 @@
         <v>0</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="b">
         <v>0</v>
@@ -38850,13 +39424,13 @@
         <v>0</v>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
       </c>
       <c r="AA14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="b">
         <v>0</v>
@@ -38877,20 +39451,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Musculoskeletal</t>
+          <t>Gastrointestinal</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3196235</v>
+        <v>3195405</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Soft tissue mass, abdomen, nonsuperficial, initial imaging</t>
+          <t>RLQ pain, initial imaging</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6964</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6314</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -38910,16 +39484,16 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="b">
         <v>1</v>
@@ -38931,10 +39505,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
@@ -38943,10 +39517,10 @@
         <v>1</v>
       </c>
       <c r="T15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="b">
         <v>0</v>
@@ -38958,13 +39532,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="b">
         <v>0</v>
       </c>
       <c r="AA15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="b">
         <v>0</v>
@@ -38985,20 +39559,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Musculoskeletal</t>
+          <t>Gastrointestinal</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3196251</v>
+        <v>3196674</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Soft tissue mass, abdomen, radiography and noncontrast US nondiagnostic, next imaging study</t>
+          <t>Sepsis suspected, acute abdominal pain, initial imaging</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6980</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7249</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -39018,7 +39592,7 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
@@ -39027,7 +39601,7 @@
         <v>1</v>
       </c>
       <c r="L16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="b">
         <v>1</v>
@@ -39036,22 +39610,22 @@
         <v>1</v>
       </c>
       <c r="O16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>
@@ -39066,13 +39640,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="b">
         <v>0</v>
       </c>
       <c r="AA16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="b">
         <v>0</v>
@@ -39093,20 +39667,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Musculoskeletal</t>
+          <t>Gastrointestinal</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3196238</v>
+        <v>3196675</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Soft tissue mass, pelvis, nonsuperficial, initial imaging</t>
+          <t>Sepsis, acute abdominal pain, initial imaging</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6967</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7250</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -39121,21 +39695,21 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelvis</t>
+          <t>Abdomen</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="b">
         <v>1</v>
@@ -39159,10 +39733,10 @@
         <v>1</v>
       </c>
       <c r="T17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="b">
         <v>0</v>
@@ -39174,13 +39748,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="b">
         <v>0</v>
       </c>
       <c r="AA17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="b">
         <v>0</v>
@@ -39201,20 +39775,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Musculoskeletal</t>
+          <t>Gastrointestinal</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3196254</v>
+        <v>3074217</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Soft tissue mass, pelvis, radiography and noncontrast US nondiagnostic, next imaging study</t>
+          <t>Small bowel obstruction suspected, acute presentation, initial imaging</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6983</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=916</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -39229,12 +39803,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelvis</t>
+          <t>Abdomen</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
@@ -39243,7 +39817,7 @@
         <v>1</v>
       </c>
       <c r="L18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="b">
         <v>1</v>
@@ -39252,13 +39826,13 @@
         <v>1</v>
       </c>
       <c r="O18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
       </c>
       <c r="Q18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
@@ -39273,7 +39847,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="b">
         <v>1</v>
@@ -39282,13 +39856,13 @@
         <v>0</v>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="b">
         <v>0</v>
       </c>
       <c r="AA18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="b">
         <v>0</v>
@@ -39309,20 +39883,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Urologic</t>
+          <t>Gastrointestinal</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3106361</v>
+        <v>3074218</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HTN, high suspicion renal vascular, decreased renal function</t>
+          <t>Small bowel obstruction suspected, intermittent or low grade, indolent presentation</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2488</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=917</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -39342,46 +39916,46 @@
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
       </c>
       <c r="O19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
       </c>
       <c r="T19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" t="b">
         <v>0</v>
       </c>
       <c r="V19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="b">
         <v>1</v>
@@ -39390,13 +39964,13 @@
         <v>0</v>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="b">
         <v>0</v>
       </c>
       <c r="AA19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="b">
         <v>0</v>
@@ -39417,20 +39991,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Urologic</t>
+          <t>Gastrointestinal</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3197008</v>
+        <v>3102193</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hydronephrosis, unknown cause, bilateral, asymptomatic, initial imaging</t>
+          <t>Upper GI bleeding suspected, nonvariceal, no endoscopy, initial imaging</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7394</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2377</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -39445,21 +40019,21 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Abdomen-pelvis</t>
+          <t>Abdomen</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="b">
         <v>1</v>
@@ -39468,10 +40042,10 @@
         <v>1</v>
       </c>
       <c r="O20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
@@ -39483,10 +40057,10 @@
         <v>0</v>
       </c>
       <c r="T20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="b">
         <v>1</v>
@@ -39498,13 +40072,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="b">
         <v>0</v>
       </c>
       <c r="AA20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="b">
         <v>0</v>
@@ -39525,20 +40099,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Urologic</t>
+          <t>Gastrointestinal</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3197009</v>
+        <v>3102196</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hydronephrosis, unknown cause, solitary kidney, asymptomatic, initial imaging</t>
+          <t>Upper GI bleeding, nonvariceal, endoscopy negative, initial imaging</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7395</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2380</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -39553,12 +40127,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Abdomen-pelvis</t>
+          <t>Abdomen</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
@@ -39567,7 +40141,7 @@
         <v>1</v>
       </c>
       <c r="L21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="b">
         <v>1</v>
@@ -39576,13 +40150,13 @@
         <v>1</v>
       </c>
       <c r="O21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="b">
         <v>1</v>
       </c>
       <c r="Q21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
@@ -39591,10 +40165,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
@@ -39606,13 +40180,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="b">
         <v>0</v>
       </c>
       <c r="AA21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="b">
         <v>0</v>
@@ -39633,20 +40207,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Urologic</t>
+          <t>Gastrointestinal</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3074313</v>
+        <v>3102195</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Renal failure, acute kidney injury, initial imaging</t>
+          <t>Upper GI bleeding, nonvariceal, no clear source on endoscopy, initial imaging</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=1006</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2379</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -39666,7 +40240,7 @@
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
@@ -39675,7 +40249,7 @@
         <v>1</v>
       </c>
       <c r="L22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="b">
         <v>1</v>
@@ -39687,16 +40261,16 @@
         <v>0</v>
       </c>
       <c r="P22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="b">
         <v>1</v>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="b">
         <v>0</v>
@@ -39714,13 +40288,13 @@
         <v>0</v>
       </c>
       <c r="Y22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="b">
         <v>0</v>
       </c>
       <c r="AA22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="b">
         <v>0</v>
@@ -39745,16 +40319,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3074314</v>
+        <v>3196626</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Renal failure, chronic kidney disease, initial imaging</t>
+          <t>Flank pain, acute, stone disease on recent imaging, recurrent symptoms, follow-up imaging</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=1007</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7218</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -39769,12 +40343,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
@@ -39783,7 +40357,7 @@
         <v>1</v>
       </c>
       <c r="L23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="b">
         <v>1</v>
@@ -39795,13 +40369,13 @@
         <v>0</v>
       </c>
       <c r="P23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="b">
         <v>1</v>
       </c>
       <c r="R23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="b">
         <v>1</v>
@@ -39813,7 +40387,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" t="b">
         <v>1</v>
@@ -39822,13 +40396,13 @@
         <v>0</v>
       </c>
       <c r="Y23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="b">
         <v>0</v>
       </c>
       <c r="AA23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="b">
         <v>0</v>
@@ -39853,16 +40427,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3194002</v>
+        <v>3196624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Renal failure, kidney disease unknown duration, initial imaging</t>
+          <t>Flank pain, acute, stone disease suspected, no hx of stone disease, initial imaging</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5495</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7217</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -39877,21 +40451,21 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="b">
         <v>1</v>
@@ -39903,13 +40477,13 @@
         <v>0</v>
       </c>
       <c r="P24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="b">
         <v>1</v>
       </c>
       <c r="R24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="b">
         <v>1</v>
@@ -39921,7 +40495,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" t="b">
         <v>1</v>
@@ -39930,13 +40504,13 @@
         <v>0</v>
       </c>
       <c r="Y24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="b">
         <v>0</v>
       </c>
       <c r="AA24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="b">
         <v>0</v>
@@ -39961,16 +40535,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3194003</v>
+        <v>3196623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Renal failure, neurogenic bladder, initial imaging</t>
+          <t>Flank pain, acute, stone disease suspected, remote hx of stone disease, initial imaging</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5496</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7216</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -39985,21 +40559,21 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="b">
         <v>1</v>
@@ -40011,19 +40585,19 @@
         <v>0</v>
       </c>
       <c r="P25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
       </c>
       <c r="R25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="b">
         <v>0</v>
@@ -40038,13 +40612,13 @@
         <v>0</v>
       </c>
       <c r="Y25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="b">
         <v>0</v>
       </c>
       <c r="AA25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="b">
         <v>0</v>
@@ -40069,16 +40643,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3084034</v>
+        <v>3195302</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Renal mass, indeterminate, contraindication to iodinated and gadolinium based contrast, initial imaging</t>
+          <t>Pyelonephritis suspected, acute, advanced age, initial imaging</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2058</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6249</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -40093,12 +40667,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
@@ -40107,28 +40681,28 @@
         <v>1</v>
       </c>
       <c r="L26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
       </c>
       <c r="O26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="b">
         <v>1</v>
       </c>
       <c r="R26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="b">
         <v>0</v>
@@ -40146,13 +40720,13 @@
         <v>0</v>
       </c>
       <c r="Y26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="b">
         <v>0</v>
       </c>
       <c r="AA26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="b">
         <v>0</v>
@@ -40177,16 +40751,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3185446</v>
+        <v>3195299</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Renal mass, indeterminate, contraindication to iodinated contrast, initial imaging</t>
+          <t>Pyelonephritis suspected, acute, complicated, initial imaging</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5397</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6246</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -40201,12 +40775,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
@@ -40215,7 +40789,7 @@
         <v>1</v>
       </c>
       <c r="L27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="b">
         <v>1</v>
@@ -40224,7 +40798,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
@@ -40233,7 +40807,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="b">
         <v>1</v>
@@ -40254,13 +40828,13 @@
         <v>0</v>
       </c>
       <c r="Y27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="b">
         <v>0</v>
       </c>
       <c r="AA27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="b">
         <v>0</v>
@@ -40281,20 +40855,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gastrointestinal</t>
+          <t>Urologic</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3102641</v>
+        <v>3195304</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Liver disease, chronic, fibrosis suspected, diagnosis and staging, initial imaging</t>
+          <t>Pyelonephritis suspected, acute, diabetes, initial imaging</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2429</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6251</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -40309,12 +40883,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
@@ -40323,7 +40897,7 @@
         <v>1</v>
       </c>
       <c r="L28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="b">
         <v>1</v>
@@ -40332,16 +40906,16 @@
         <v>1</v>
       </c>
       <c r="O28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
       </c>
       <c r="Q28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="b">
         <v>1</v>
@@ -40362,13 +40936,13 @@
         <v>0</v>
       </c>
       <c r="Y28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="b">
         <v>0</v>
       </c>
       <c r="AA28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="b">
         <v>0</v>
@@ -40389,20 +40963,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gastrointestinal</t>
+          <t>Urologic</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3196679</v>
+        <v>3195303</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sepsis suspected, cannot assess symptoms, initial imaging</t>
+          <t>Pyelonephritis suspected, acute, immune compromise, initial imaging</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7253</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6250</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -40417,12 +40991,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
@@ -40431,7 +41005,7 @@
         <v>1</v>
       </c>
       <c r="L29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="b">
         <v>1</v>
@@ -40443,7 +41017,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="b">
         <v>1</v>
@@ -40458,7 +41032,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" t="b">
         <v>0</v>
@@ -40470,13 +41044,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="b">
         <v>0</v>
       </c>
       <c r="AA29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="b">
         <v>0</v>
@@ -40497,20 +41071,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gastrointestinal</t>
+          <t>Urologic</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3196677</v>
+        <v>3195300</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sepsis suspected, non specific symptoms, unknown origin, initial imaging</t>
+          <t>Pyelonephritis suspected, acute, lack of response to initial therapy, initial imaging</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7251</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6247</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -40525,12 +41099,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
@@ -40539,7 +41113,7 @@
         <v>1</v>
       </c>
       <c r="L30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="b">
         <v>1</v>
@@ -40551,7 +41125,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="b">
         <v>1</v>
@@ -40566,7 +41140,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" t="b">
         <v>0</v>
@@ -40578,13 +41152,13 @@
         <v>0</v>
       </c>
       <c r="Y30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="b">
         <v>0</v>
       </c>
       <c r="AA30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="b">
         <v>0</v>
@@ -40605,20 +41179,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gastrointestinal</t>
+          <t>Urologic</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3196680</v>
+        <v>3195305</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sepsis, cannot assess symptoms, initial imaging</t>
+          <t>Pyelonephritis suspected, acute, recurrent pyelonephritis, initial imaging</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7254</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6252</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -40633,12 +41207,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
@@ -40647,7 +41221,7 @@
         <v>1</v>
       </c>
       <c r="L31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="b">
         <v>1</v>
@@ -40659,7 +41233,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="b">
         <v>1</v>
@@ -40674,7 +41248,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="b">
         <v>0</v>
@@ -40686,13 +41260,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="b">
         <v>0</v>
       </c>
       <c r="AA31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="b">
         <v>0</v>
@@ -40713,20 +41287,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gastrointestinal</t>
+          <t>Urologic</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3196678</v>
+        <v>3195307</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sepsis, non specific symptoms, unknown origin, initial imaging</t>
+          <t>Pyelonephritis suspected, acute, renal obstruction hx, initial imaging</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7252</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6253</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -40741,12 +41315,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
@@ -40755,7 +41329,7 @@
         <v>1</v>
       </c>
       <c r="L32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="b">
         <v>1</v>
@@ -40767,7 +41341,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="b">
         <v>1</v>
@@ -40782,7 +41356,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="b">
         <v>0</v>
@@ -40794,13 +41368,13 @@
         <v>0</v>
       </c>
       <c r="Y32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="b">
         <v>0</v>
       </c>
       <c r="AA32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="b">
         <v>0</v>
@@ -40821,20 +41395,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Polytrauma</t>
+          <t>Urologic</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3164890</v>
+        <v>3195308</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Polytrauma, blunt, hemodynamically unstable, initial imaging</t>
+          <t>Pyelonephritis suspected, acute, renal stones hx, initial imaging</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5204</t>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6254</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -40849,24 +41423,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Abdomen-pelvis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -40875,40 +41449,40 @@
         <v>0</v>
       </c>
       <c r="P33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="b">
         <v>1</v>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" t="b">
         <v>0</v>
       </c>
       <c r="U33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" t="b">
         <v>0</v>
       </c>
       <c r="W33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" t="b">
         <v>0</v>
       </c>
       <c r="Y33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="b">
         <v>0</v>
       </c>
       <c r="AA33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="b">
         <v>0</v>
@@ -40923,6 +41497,1518 @@
         <v>0</v>
       </c>
       <c r="AF33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Urologic</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3195301</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Pyelonephritis suspected, acute, vesicoureteral reflux, initial imaging</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6248</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Abdomen-pelvis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" t="b">
+        <v>1</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="b">
+        <v>0</v>
+      </c>
+      <c r="U34" t="b">
+        <v>0</v>
+      </c>
+      <c r="V34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W34" t="b">
+        <v>1</v>
+      </c>
+      <c r="X34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Vascular</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3194260</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Retroperitoneal bleed suspected, initial imaging</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5605</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Abdomen-pelvis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
+      </c>
+      <c r="O35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="b">
+        <v>1</v>
+      </c>
+      <c r="U35" t="b">
+        <v>0</v>
+      </c>
+      <c r="V35" t="b">
+        <v>1</v>
+      </c>
+      <c r="W35" t="b">
+        <v>1</v>
+      </c>
+      <c r="X35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3196683</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sepsis suspected, non specific symptoms, unknown origin, chest radiography equivocal, next imaging study</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7256</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="b">
+        <v>0</v>
+      </c>
+      <c r="U36" t="b">
+        <v>0</v>
+      </c>
+      <c r="V36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W36" t="b">
+        <v>1</v>
+      </c>
+      <c r="X36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3196684</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sepsis suspected, non specific symptoms, unknown origin, chest radiography nonspecific, next imaging study</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7257</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U37" t="b">
+        <v>0</v>
+      </c>
+      <c r="V37" t="b">
+        <v>0</v>
+      </c>
+      <c r="W37" t="b">
+        <v>1</v>
+      </c>
+      <c r="X37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3196682</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sepsis suspected, non specific symptoms, unknown origin, chest radiography normal, next imaging study</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7255</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
+      </c>
+      <c r="O38" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U38" t="b">
+        <v>0</v>
+      </c>
+      <c r="V38" t="b">
+        <v>0</v>
+      </c>
+      <c r="W38" t="b">
+        <v>1</v>
+      </c>
+      <c r="X38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3196689</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sepsis suspected, cannot assess symptoms, chest radiography equivocal, next imaging study</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7262</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="b">
+        <v>0</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="b">
+        <v>0</v>
+      </c>
+      <c r="U39" t="b">
+        <v>0</v>
+      </c>
+      <c r="V39" t="b">
+        <v>0</v>
+      </c>
+      <c r="W39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3196690</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sepsis suspected, cannot assess symptoms, chest radiography nonspecific, next imaging study</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7263</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="b">
+        <v>0</v>
+      </c>
+      <c r="U40" t="b">
+        <v>0</v>
+      </c>
+      <c r="V40" t="b">
+        <v>0</v>
+      </c>
+      <c r="W40" t="b">
+        <v>1</v>
+      </c>
+      <c r="X40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3196688</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sepsis suspected, cannot assess symptoms, chest radiography normal, next imaging study</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7261</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" t="b">
+        <v>1</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="b">
+        <v>0</v>
+      </c>
+      <c r="U41" t="b">
+        <v>0</v>
+      </c>
+      <c r="V41" t="b">
+        <v>0</v>
+      </c>
+      <c r="W41" t="b">
+        <v>1</v>
+      </c>
+      <c r="X41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3196691</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sepsis, cannot assess symptoms, chest radiography normal, next imaging study</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7264</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" t="b">
+        <v>1</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" t="b">
+        <v>0</v>
+      </c>
+      <c r="P42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="b">
+        <v>1</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="b">
+        <v>0</v>
+      </c>
+      <c r="U42" t="b">
+        <v>0</v>
+      </c>
+      <c r="V42" t="b">
+        <v>0</v>
+      </c>
+      <c r="W42" t="b">
+        <v>1</v>
+      </c>
+      <c r="X42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3196692</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sepsis, cannot assess symptoms, chest radiography equivocal, next imaging study</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7265</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="b">
+        <v>0</v>
+      </c>
+      <c r="M43" t="b">
+        <v>1</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
+      </c>
+      <c r="O43" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="b">
+        <v>1</v>
+      </c>
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="b">
+        <v>0</v>
+      </c>
+      <c r="U43" t="b">
+        <v>0</v>
+      </c>
+      <c r="V43" t="b">
+        <v>0</v>
+      </c>
+      <c r="W43" t="b">
+        <v>1</v>
+      </c>
+      <c r="X43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3196693</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sepsis, cannot assess symptoms, chest radiography nonspecific, next imaging study</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7266</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="b">
+        <v>0</v>
+      </c>
+      <c r="M44" t="b">
+        <v>1</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="b">
+        <v>1</v>
+      </c>
+      <c r="R44" t="b">
+        <v>0</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="b">
+        <v>0</v>
+      </c>
+      <c r="U44" t="b">
+        <v>0</v>
+      </c>
+      <c r="V44" t="b">
+        <v>0</v>
+      </c>
+      <c r="W44" t="b">
+        <v>1</v>
+      </c>
+      <c r="X44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3196686</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sepsis, non specific symptoms, unknown origin, chest radiography equivocal, next imaging study</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7259</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
+      </c>
+      <c r="O45" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="b">
+        <v>1</v>
+      </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="b">
+        <v>0</v>
+      </c>
+      <c r="U45" t="b">
+        <v>0</v>
+      </c>
+      <c r="V45" t="b">
+        <v>0</v>
+      </c>
+      <c r="W45" t="b">
+        <v>1</v>
+      </c>
+      <c r="X45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3196687</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sepsis, non specific symptoms, unknown origin, chest radiography nonspecific, next imaging study</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7260</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" t="b">
+        <v>1</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
+      </c>
+      <c r="O46" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="b">
+        <v>1</v>
+      </c>
+      <c r="R46" t="b">
+        <v>0</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="b">
+        <v>0</v>
+      </c>
+      <c r="U46" t="b">
+        <v>0</v>
+      </c>
+      <c r="V46" t="b">
+        <v>0</v>
+      </c>
+      <c r="W46" t="b">
+        <v>1</v>
+      </c>
+      <c r="X46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3196685</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Sepsis, non specific symptoms, unknown origin, chest radiography normal, next imaging study</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7258</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" t="b">
+        <v>1</v>
+      </c>
+      <c r="N47" t="b">
+        <v>1</v>
+      </c>
+      <c r="O47" t="b">
+        <v>0</v>
+      </c>
+      <c r="P47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="b">
+        <v>1</v>
+      </c>
+      <c r="R47" t="b">
+        <v>0</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="b">
+        <v>0</v>
+      </c>
+      <c r="U47" t="b">
+        <v>0</v>
+      </c>
+      <c r="V47" t="b">
+        <v>0</v>
+      </c>
+      <c r="W47" t="b">
+        <v>1</v>
+      </c>
+      <c r="X47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="b">
         <v>0</v>
       </c>
     </row>
@@ -40937,6 +43023,4490 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AF3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>scenario-id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>scenario-text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>scenario-url</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>body-area</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>priority-clinical-areas</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ct_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ct_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ct_not_appropriate</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>other_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>other_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>other_not_appropriate</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>mr_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>mr_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mr_not_appropriate</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>us_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>us_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>us_not_appropriate</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>other_modality_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>other_modality_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>other_modality_not_appropriate</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>green-green</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>green-yellow</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>green-red</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>yellow-green</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>yellow-yellow</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>yellow-red</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>red-green</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>red-yellow</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>red-red</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Musculoskeletal</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3196267</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Soft tissue mass, abdomen, radiography and noncontrast US nondiagnostic, MRI contraindicated, next imaging study</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6996</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Musculoskeletal</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3196270</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Soft tissue mass, pelvis, radiography and noncontrast US nondiagnostic, MRI contraindicated, next imaging study</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6999</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pelvis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>scenario-id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>scenario-text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>scenario-url</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>body-area</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>priority-clinical-areas</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ct_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ct_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ct_not_appropriate</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>other_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>other_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>other_not_appropriate</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>mr_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>mr_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mr_not_appropriate</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>us_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>us_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>us_not_appropriate</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>other_modality_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>other_modality_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>other_modality_not_appropriate</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>green-green</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>green-yellow</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>green-red</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>yellow-green</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>yellow-yellow</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>yellow-red</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>red-green</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>red-yellow</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>red-red</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3196526</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Abnormal liver function tests, hepatocellular predominance, mild aminotransferase increase , initial imaging</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7151</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3194197</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Epigastric pain, acid reflux suspected, initial imaging</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5564</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3194201</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Epigastric pain, duodenal ulcer suspected, initial imaging</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5568</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>1</v>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3194198</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Epigastric pain, esophagitis suspected, initial imaging</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5565</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>1</v>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="b">
+        <v>1</v>
+      </c>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3194199</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Epigastric pain, gastritis suspected, initial imaging</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5566</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>1</v>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3194200</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Epigastric pain, peptic ulcer suspected, initial imaging</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5567</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>1</v>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3100710</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Liver lesion, &lt;1cm, indeterminate on US, hx of extrahepatic malignancy</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2164</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" t="b">
+        <v>1</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3084079</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pancreatitis suspected, typical presentation</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2103</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3195883</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RUQ pain, acalculous cholecystitis suspected, US equivocal, next imaging study</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6707</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>1</v>
+      </c>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3195882</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RUQ pain, acalculous cholecystitis suspected, US negative, next imaging study</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6706</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" t="b">
+        <v>1</v>
+      </c>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3195877</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RUQ pain, biliary disease suspected, initial imaging</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6701</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" t="b">
+        <v>1</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gyn and OB</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3074377</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pelvic pain, acute, negative beta-hCG, gynecological etiology suspected, initial imaging</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=1042</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Female Only</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10 - 60</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pelvis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gyn and OB</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3148178</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pelvic pain, chronic, post-menopausal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=4553</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Female Only</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pelvis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" t="b">
+        <v>1</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Musculoskeletal</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3196235</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Soft tissue mass, abdomen, nonsuperficial, initial imaging</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6964</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" t="b">
+        <v>1</v>
+      </c>
+      <c r="V15" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15" t="b">
+        <v>1</v>
+      </c>
+      <c r="X15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Musculoskeletal</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3196251</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Soft tissue mass, abdomen, radiography and noncontrast US nondiagnostic, next imaging study</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6980</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16" t="b">
+        <v>1</v>
+      </c>
+      <c r="X16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Musculoskeletal</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3196238</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Soft tissue mass, pelvis, nonsuperficial, initial imaging</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6967</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pelvis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="b">
+        <v>1</v>
+      </c>
+      <c r="U17" t="b">
+        <v>1</v>
+      </c>
+      <c r="V17" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" t="b">
+        <v>1</v>
+      </c>
+      <c r="X17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Musculoskeletal</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3196254</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Soft tissue mass, pelvis, radiography and noncontrast US nondiagnostic, next imaging study</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=6983</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pelvis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="b">
+        <v>1</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Urologic</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3106361</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HTN, high suspicion renal vascular, decreased renal function</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2488</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="b">
+        <v>1</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W19" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Urologic</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3197008</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Hydronephrosis, unknown cause, bilateral, asymptomatic, initial imaging</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7394</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Abdomen-pelvis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="b">
+        <v>1</v>
+      </c>
+      <c r="U20" t="b">
+        <v>1</v>
+      </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Urologic</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3197009</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Hydronephrosis, unknown cause, solitary kidney, asymptomatic, initial imaging</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7395</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Abdomen-pelvis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="b">
+        <v>1</v>
+      </c>
+      <c r="U21" t="b">
+        <v>1</v>
+      </c>
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="W21" t="b">
+        <v>1</v>
+      </c>
+      <c r="X21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Urologic</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3074313</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Renal failure, acute kidney injury, initial imaging</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=1006</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="b">
+        <v>1</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="W22" t="b">
+        <v>1</v>
+      </c>
+      <c r="X22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Urologic</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3074314</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Renal failure, chronic kidney disease, initial imaging</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=1007</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" t="b">
+        <v>1</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="b">
+        <v>1</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" t="b">
+        <v>0</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" t="b">
+        <v>1</v>
+      </c>
+      <c r="X23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Urologic</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3194002</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Renal failure, kidney disease unknown duration, initial imaging</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5495</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="b">
+        <v>1</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
+      </c>
+      <c r="O24" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="b">
+        <v>1</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
+        <v>0</v>
+      </c>
+      <c r="V24" t="b">
+        <v>0</v>
+      </c>
+      <c r="W24" t="b">
+        <v>1</v>
+      </c>
+      <c r="X24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Urologic</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3194003</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Renal failure, neurogenic bladder, initial imaging</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5496</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
+      </c>
+      <c r="O25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="b">
+        <v>1</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="b">
+        <v>1</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="b">
+        <v>1</v>
+      </c>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Urologic</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3084034</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Renal mass, indeterminate, contraindication to iodinated and gadolinium based contrast, initial imaging</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2058</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
+      </c>
+      <c r="O26" t="b">
+        <v>1</v>
+      </c>
+      <c r="P26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="b">
+        <v>1</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" t="b">
+        <v>1</v>
+      </c>
+      <c r="X26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Urologic</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3185446</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Renal mass, indeterminate, contraindication to iodinated contrast, initial imaging</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5397</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27" t="b">
+        <v>1</v>
+      </c>
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" t="b">
+        <v>0</v>
+      </c>
+      <c r="W27" t="b">
+        <v>1</v>
+      </c>
+      <c r="X27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3102641</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Liver disease, chronic, fibrosis suspected, diagnosis and staging, initial imaging</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=2429</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
+      </c>
+      <c r="O28" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28" t="b">
+        <v>1</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
+        <v>0</v>
+      </c>
+      <c r="V28" t="b">
+        <v>0</v>
+      </c>
+      <c r="W28" t="b">
+        <v>1</v>
+      </c>
+      <c r="X28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3196679</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sepsis suspected, cannot assess symptoms, initial imaging</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7253</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" t="b">
+        <v>1</v>
+      </c>
+      <c r="V29" t="b">
+        <v>0</v>
+      </c>
+      <c r="W29" t="b">
+        <v>1</v>
+      </c>
+      <c r="X29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3196677</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sepsis suspected, non specific symptoms, unknown origin, initial imaging</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7251</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="b">
+        <v>1</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
+      </c>
+      <c r="O30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3196680</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sepsis, cannot assess symptoms, initial imaging</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7254</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="b">
+        <v>1</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O31" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" t="b">
+        <v>1</v>
+      </c>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" t="b">
+        <v>1</v>
+      </c>
+      <c r="X31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Gastrointestinal</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3196678</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sepsis, non specific symptoms, unknown origin, initial imaging</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7252</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="b">
+        <v>1</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
+      </c>
+      <c r="O32" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" t="b">
+        <v>1</v>
+      </c>
+      <c r="V32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32" t="b">
+        <v>1</v>
+      </c>
+      <c r="X32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Polytrauma</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3164890</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Polytrauma, blunt, hemodynamically unstable, initial imaging</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=5204</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O33" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="b">
+        <v>1</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33" t="b">
+        <v>1</v>
+      </c>
+      <c r="V33" t="b">
+        <v>0</v>
+      </c>
+      <c r="W33" t="b">
+        <v>0</v>
+      </c>
+      <c r="X33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>scenario-id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>scenario-text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>scenario-url</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>body-area</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>priority-clinical-areas</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ct_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ct_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ct_not_appropriate</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>other_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>other_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>other_not_appropriate</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>mr_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>mr_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mr_not_appropriate</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>us_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>us_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>us_not_appropriate</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>other_modality_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>other_modality_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>other_modality_not_appropriate</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>green-green</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>green-yellow</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>green-red</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>yellow-green</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>yellow-yellow</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>yellow-red</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>red-green</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>red-yellow</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>red-red</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Urologic</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3196631</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Flank pain, acute, stone disease suspected, CT without contrast inconclusive for stones, next imaging study</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://gravitas.acr.org/ACPortal/GetDataForOneScenario?senarioId=7221</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>18 - 150</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Abdomen-pelvis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>scenario-id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>scenario-text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>scenario-url</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>body-area</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>priority-clinical-areas</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ct_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ct_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ct_not_appropriate</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>other_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>other_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>other_not_appropriate</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>mr_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>mr_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mr_not_appropriate</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>us_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>us_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>us_not_appropriate</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>other_modality_usually_appropriate</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>other_modality_may_be_appropriate</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>other_modality_not_appropriate</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>green-green</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>green-yellow</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>green-red</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>yellow-green</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>yellow-yellow</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>yellow-red</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>red-green</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>red-yellow</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>red-red</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AF26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
